--- a/public/TalentData/talents (2).xlsx
+++ b/public/TalentData/talents (2).xlsx
@@ -168,10 +168,10 @@
     <t>Tidak Aktif</t>
   </si>
   <si>
-    <t>2 test talent</t>
-  </si>
-  <si>
-    <t>2test-talent@gmail.com</t>
+    <t>1test-talent@gmail.com</t>
+  </si>
+  <si>
+    <t>1 test talent</t>
   </si>
 </sst>
 </file>
@@ -276,7 +276,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -311,7 +311,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -632,10 +632,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="D2" t="s">
         <v>34</v>
